--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-evaluation.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-evaluation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7366" uniqueCount="596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7366" uniqueCount="597">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -851,6 +851,10 @@
   </si>
   <si>
     <t>ED.thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
   </si>
   <si>
     <t>Observation.statusCode</t>
@@ -8754,7 +8758,7 @@
         <v>74</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>74</v>
+        <v>273</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>74</v>
@@ -8762,10 +8766,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8791,10 +8795,10 @@
         <v>91</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8825,7 +8829,7 @@
       </c>
       <c r="Y65" s="2"/>
       <c r="Z65" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>74</v>
@@ -8843,7 +8847,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -8863,10 +8867,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8964,10 +8968,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9008,7 +9012,7 @@
         <v>74</v>
       </c>
       <c r="S67" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="T67" t="s" s="2">
         <v>74</v>
@@ -9067,10 +9071,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9170,10 +9174,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9273,10 +9277,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9376,10 +9380,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9479,10 +9483,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9580,10 +9584,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9681,10 +9685,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9784,10 +9788,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9887,10 +9891,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9990,10 +9994,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10016,7 +10020,7 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L77" t="s" s="2">
         <v>13</v>
@@ -10073,7 +10077,7 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -10093,10 +10097,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10119,7 +10123,7 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
@@ -10152,7 +10156,7 @@
       </c>
       <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>74</v>
@@ -10170,7 +10174,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -10190,10 +10194,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10216,7 +10220,7 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
@@ -10269,7 +10273,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -10289,10 +10293,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10348,25 +10352,25 @@
       </c>
       <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF80" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -10386,10 +10390,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10415,10 +10419,10 @@
         <v>179</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -10469,7 +10473,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -10489,10 +10493,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10515,13 +10519,13 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -10552,7 +10556,7 @@
       </c>
       <c r="Y82" s="2"/>
       <c r="Z82" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>74</v>
@@ -10570,7 +10574,7 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -10590,10 +10594,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10616,7 +10620,7 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
@@ -10649,25 +10653,25 @@
       </c>
       <c r="Y83" s="2"/>
       <c r="Z83" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF83" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -10687,10 +10691,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10717,7 +10721,7 @@
       </c>
       <c r="L84" s="2"/>
       <c r="M84" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -10768,7 +10772,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -10788,10 +10792,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10814,7 +10818,7 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
@@ -10867,7 +10871,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -10887,10 +10891,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10913,7 +10917,7 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
@@ -10966,7 +10970,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10986,10 +10990,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11012,13 +11016,13 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -11069,7 +11073,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -11089,10 +11093,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11115,13 +11119,13 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -11172,7 +11176,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -11192,10 +11196,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11218,7 +11222,7 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
@@ -11271,7 +11275,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -11291,10 +11295,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11317,13 +11321,13 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -11374,7 +11378,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -11394,10 +11398,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11495,10 +11499,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11596,10 +11600,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11697,10 +11701,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11798,10 +11802,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11901,10 +11905,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12004,10 +12008,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12107,10 +12111,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12210,10 +12214,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12239,7 +12243,7 @@
         <v>95</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M99" t="s" s="2">
         <v>122</v>
@@ -12311,13 +12315,13 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D100" t="s" s="2">
         <v>74</v>
@@ -12342,10 +12346,10 @@
         <v>95</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -12416,10 +12420,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12517,10 +12521,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12620,10 +12624,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12723,10 +12727,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12767,7 +12771,7 @@
         <v>74</v>
       </c>
       <c r="S104" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="T104" t="s" s="2">
         <v>74</v>
@@ -12826,10 +12830,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12929,13 +12933,13 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D106" t="s" s="2">
         <v>74</v>
@@ -12960,10 +12964,10 @@
         <v>95</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -13034,10 +13038,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13074,7 +13078,7 @@
         <v>74</v>
       </c>
       <c r="S107" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="T107" t="s" s="2">
         <v>74</v>
@@ -13093,7 +13097,7 @@
       </c>
       <c r="Y107" s="2"/>
       <c r="Z107" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>74</v>
@@ -13111,7 +13115,7 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>75</v>
@@ -13131,10 +13135,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13168,7 +13172,7 @@
       </c>
       <c r="Q108" s="2"/>
       <c r="R108" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="S108" t="s" s="2">
         <v>74</v>
@@ -13190,7 +13194,7 @@
       </c>
       <c r="Y108" s="2"/>
       <c r="Z108" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>74</v>
@@ -13208,7 +13212,7 @@
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -13228,10 +13232,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13254,7 +13258,7 @@
         <v>74</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
@@ -13307,7 +13311,7 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -13327,10 +13331,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13353,13 +13357,13 @@
         <v>74</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -13410,7 +13414,7 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -13430,10 +13434,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13531,10 +13535,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13557,11 +13561,11 @@
         <v>74</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L112" s="2"/>
       <c r="M112" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -13612,7 +13616,7 @@
         <v>74</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -13632,10 +13636,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13662,12 +13666,12 @@
       </c>
       <c r="L113" s="2"/>
       <c r="M113" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q113" s="2"/>
       <c r="R113" t="s" s="2">
@@ -13693,7 +13697,7 @@
       </c>
       <c r="Y113" s="2"/>
       <c r="Z113" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>74</v>
@@ -13711,7 +13715,7 @@
         <v>74</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -13731,17 +13735,17 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E114" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F114" t="s" s="2">
         <v>80</v>
@@ -13759,11 +13763,11 @@
         <v>74</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L114" s="2"/>
       <c r="M114" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -13814,7 +13818,7 @@
         <v>74</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -13834,17 +13838,17 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E115" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F115" t="s" s="2">
         <v>80</v>
@@ -13862,11 +13866,11 @@
         <v>74</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L115" s="2"/>
       <c r="M115" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -13917,7 +13921,7 @@
         <v>74</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -13937,17 +13941,17 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E116" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F116" t="s" s="2">
         <v>80</v>
@@ -13965,11 +13969,11 @@
         <v>74</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L116" s="2"/>
       <c r="M116" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -14020,7 +14024,7 @@
         <v>74</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -14040,17 +14044,17 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E117" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F117" t="s" s="2">
         <v>80</v>
@@ -14068,11 +14072,11 @@
         <v>74</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L117" s="2"/>
       <c r="M117" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -14123,7 +14127,7 @@
         <v>74</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -14143,10 +14147,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14169,7 +14173,7 @@
         <v>74</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L118" s="2"/>
       <c r="M118" s="2"/>
@@ -14222,7 +14226,7 @@
         <v>74</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -14242,10 +14246,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -14268,13 +14272,13 @@
         <v>74</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -14325,7 +14329,7 @@
         <v>74</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>75</v>
@@ -14345,10 +14349,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -14371,7 +14375,7 @@
         <v>74</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L120" s="2"/>
       <c r="M120" s="2"/>
@@ -14412,7 +14416,7 @@
         <v>74</v>
       </c>
       <c r="AB120" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AC120" s="2"/>
       <c r="AD120" t="s" s="2">
@@ -14422,7 +14426,7 @@
         <v>124</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -14442,13 +14446,13 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D121" t="s" s="2">
         <v>74</v>
@@ -14470,7 +14474,7 @@
         <v>74</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L121" s="2"/>
       <c r="M121" s="2"/>
@@ -14523,7 +14527,7 @@
         <v>74</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -14543,10 +14547,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14644,10 +14648,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14745,10 +14749,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14846,10 +14850,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14947,10 +14951,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -15050,10 +15054,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -15153,10 +15157,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -15256,10 +15260,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -15359,10 +15363,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -15460,10 +15464,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -15500,7 +15504,7 @@
         <v>74</v>
       </c>
       <c r="S131" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="T131" t="s" s="2">
         <v>74</v>
@@ -15519,7 +15523,7 @@
       </c>
       <c r="Y131" s="2"/>
       <c r="Z131" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>74</v>
@@ -15537,7 +15541,7 @@
         <v>74</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>75</v>
@@ -15557,10 +15561,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15587,7 +15591,7 @@
       </c>
       <c r="L132" s="2"/>
       <c r="M132" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -15638,7 +15642,7 @@
         <v>74</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -15658,10 +15662,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15688,12 +15692,12 @@
       </c>
       <c r="L133" s="2"/>
       <c r="M133" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q133" s="2"/>
       <c r="R133" t="s" s="2">
@@ -15739,7 +15743,7 @@
         <v>74</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -15759,10 +15763,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15838,7 +15842,7 @@
         <v>74</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -15858,10 +15862,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -15884,7 +15888,7 @@
         <v>74</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L135" s="2"/>
       <c r="M135" s="2"/>
@@ -15937,7 +15941,7 @@
         <v>74</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -15957,10 +15961,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -15983,7 +15987,7 @@
         <v>74</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L136" s="2"/>
       <c r="M136" s="2"/>
@@ -16036,7 +16040,7 @@
         <v>74</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -16056,10 +16060,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -16082,7 +16086,7 @@
         <v>74</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L137" s="2"/>
       <c r="M137" s="2"/>
@@ -16135,7 +16139,7 @@
         <v>74</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -16155,10 +16159,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -16181,7 +16185,7 @@
         <v>74</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L138" s="2"/>
       <c r="M138" s="2"/>
@@ -16234,7 +16238,7 @@
         <v>74</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -16254,10 +16258,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -16280,7 +16284,7 @@
         <v>74</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L139" s="2"/>
       <c r="M139" s="2"/>
@@ -16333,7 +16337,7 @@
         <v>74</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -16353,10 +16357,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -16379,7 +16383,7 @@
         <v>74</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L140" s="2"/>
       <c r="M140" s="2"/>
@@ -16432,7 +16436,7 @@
         <v>74</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -16452,10 +16456,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -16478,7 +16482,7 @@
         <v>74</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L141" s="2"/>
       <c r="M141" s="2"/>
@@ -16531,7 +16535,7 @@
         <v>74</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
@@ -16551,10 +16555,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -16577,7 +16581,7 @@
         <v>74</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L142" s="2"/>
       <c r="M142" s="2"/>
@@ -16630,7 +16634,7 @@
         <v>74</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>80</v>
@@ -16650,10 +16654,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -16676,7 +16680,7 @@
         <v>74</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L143" s="2"/>
       <c r="M143" s="2"/>
@@ -16729,7 +16733,7 @@
         <v>74</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -16749,10 +16753,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -16775,7 +16779,7 @@
         <v>74</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="L144" s="2"/>
       <c r="M144" s="2"/>
@@ -16828,7 +16832,7 @@
         <v>74</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -16848,10 +16852,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -16874,7 +16878,7 @@
         <v>74</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L145" s="2"/>
       <c r="M145" s="2"/>
@@ -16927,7 +16931,7 @@
         <v>74</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -16947,13 +16951,13 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D146" t="s" s="2">
         <v>74</v>
@@ -16975,10 +16979,10 @@
         <v>74</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M146" s="2"/>
       <c r="N146" s="2"/>
@@ -17030,7 +17034,7 @@
         <v>74</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
@@ -17050,10 +17054,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -17151,10 +17155,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -17252,10 +17256,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -17353,10 +17357,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -17454,10 +17458,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -17557,10 +17561,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -17660,10 +17664,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -17763,10 +17767,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -17866,10 +17870,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -17967,10 +17971,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -18007,7 +18011,7 @@
         <v>74</v>
       </c>
       <c r="S156" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="T156" t="s" s="2">
         <v>74</v>
@@ -18026,7 +18030,7 @@
       </c>
       <c r="Y156" s="2"/>
       <c r="Z156" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>74</v>
@@ -18044,7 +18048,7 @@
         <v>74</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>75</v>
@@ -18064,10 +18068,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -18094,7 +18098,7 @@
       </c>
       <c r="L157" s="2"/>
       <c r="M157" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
@@ -18145,7 +18149,7 @@
         <v>74</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
@@ -18165,10 +18169,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -18195,12 +18199,12 @@
       </c>
       <c r="L158" s="2"/>
       <c r="M158" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q158" s="2"/>
       <c r="R158" t="s" s="2">
@@ -18246,7 +18250,7 @@
         <v>74</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -18266,10 +18270,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -18345,7 +18349,7 @@
         <v>74</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -18365,10 +18369,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -18391,7 +18395,7 @@
         <v>74</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L160" s="2"/>
       <c r="M160" s="2"/>
@@ -18444,7 +18448,7 @@
         <v>74</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -18464,10 +18468,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -18490,7 +18494,7 @@
         <v>74</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L161" s="2"/>
       <c r="M161" s="2"/>
@@ -18543,7 +18547,7 @@
         <v>74</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
@@ -18563,10 +18567,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -18589,7 +18593,7 @@
         <v>74</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L162" s="2"/>
       <c r="M162" s="2"/>
@@ -18642,7 +18646,7 @@
         <v>74</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -18662,10 +18666,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -18688,7 +18692,7 @@
         <v>74</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L163" s="2"/>
       <c r="M163" s="2"/>
@@ -18741,7 +18745,7 @@
         <v>74</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -18761,10 +18765,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -18787,7 +18791,7 @@
         <v>74</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L164" s="2"/>
       <c r="M164" s="2"/>
@@ -18840,7 +18844,7 @@
         <v>74</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -18860,10 +18864,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -18886,7 +18890,7 @@
         <v>74</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L165" s="2"/>
       <c r="M165" s="2"/>
@@ -18939,7 +18943,7 @@
         <v>74</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -18959,10 +18963,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -18985,7 +18989,7 @@
         <v>74</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L166" s="2"/>
       <c r="M166" s="2"/>
@@ -19038,7 +19042,7 @@
         <v>74</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -19058,10 +19062,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -19084,7 +19088,7 @@
         <v>74</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L167" s="2"/>
       <c r="M167" s="2"/>
@@ -19137,7 +19141,7 @@
         <v>74</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -19157,10 +19161,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -19183,7 +19187,7 @@
         <v>74</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L168" s="2"/>
       <c r="M168" s="2"/>
@@ -19236,7 +19240,7 @@
         <v>74</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -19256,10 +19260,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -19282,7 +19286,7 @@
         <v>74</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="L169" s="2"/>
       <c r="M169" s="2"/>
@@ -19335,7 +19339,7 @@
         <v>74</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
@@ -19355,10 +19359,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -19381,7 +19385,7 @@
         <v>74</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L170" s="2"/>
       <c r="M170" s="2"/>
@@ -19434,7 +19438,7 @@
         <v>74</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>80</v>
@@ -19454,13 +19458,13 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D171" t="s" s="2">
         <v>74</v>
@@ -19482,10 +19486,10 @@
         <v>74</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M171" s="2"/>
       <c r="N171" s="2"/>
@@ -19537,7 +19541,7 @@
         <v>74</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>80</v>
@@ -19557,10 +19561,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -19658,10 +19662,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -19759,10 +19763,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -19860,10 +19864,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -19961,10 +19965,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -20064,10 +20068,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -20167,10 +20171,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -20270,10 +20274,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -20373,10 +20377,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -20474,10 +20478,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -20514,7 +20518,7 @@
         <v>74</v>
       </c>
       <c r="S181" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="T181" t="s" s="2">
         <v>74</v>
@@ -20533,7 +20537,7 @@
       </c>
       <c r="Y181" s="2"/>
       <c r="Z181" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AA181" t="s" s="2">
         <v>74</v>
@@ -20551,7 +20555,7 @@
         <v>74</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>75</v>
@@ -20571,10 +20575,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -20601,7 +20605,7 @@
       </c>
       <c r="L182" s="2"/>
       <c r="M182" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N182" s="2"/>
       <c r="O182" s="2"/>
@@ -20613,7 +20617,7 @@
         <v>74</v>
       </c>
       <c r="S182" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="T182" t="s" s="2">
         <v>74</v>
@@ -20652,7 +20656,7 @@
         <v>74</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>80</v>
@@ -20672,10 +20676,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -20702,12 +20706,12 @@
       </c>
       <c r="L183" s="2"/>
       <c r="M183" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" s="2"/>
       <c r="P183" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q183" s="2"/>
       <c r="R183" t="s" s="2">
@@ -20753,7 +20757,7 @@
         <v>74</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -20773,10 +20777,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -20852,7 +20856,7 @@
         <v>74</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>80</v>
@@ -20872,10 +20876,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -20898,7 +20902,7 @@
         <v>74</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L185" s="2"/>
       <c r="M185" s="2"/>
@@ -20951,7 +20955,7 @@
         <v>74</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>80</v>
@@ -20971,10 +20975,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -20997,7 +21001,7 @@
         <v>74</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L186" s="2"/>
       <c r="M186" s="2"/>
@@ -21050,7 +21054,7 @@
         <v>74</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>80</v>
@@ -21070,10 +21074,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -21096,7 +21100,7 @@
         <v>74</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="L187" s="2"/>
       <c r="M187" s="2"/>
@@ -21149,7 +21153,7 @@
         <v>74</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>80</v>
@@ -21169,10 +21173,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -21195,7 +21199,7 @@
         <v>74</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L188" s="2"/>
       <c r="M188" s="2"/>
@@ -21248,7 +21252,7 @@
         <v>74</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>80</v>
@@ -21268,10 +21272,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -21294,7 +21298,7 @@
         <v>74</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="L189" s="2"/>
       <c r="M189" s="2"/>
@@ -21347,7 +21351,7 @@
         <v>74</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>80</v>
@@ -21367,10 +21371,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -21393,7 +21397,7 @@
         <v>74</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L190" s="2"/>
       <c r="M190" s="2"/>
@@ -21446,7 +21450,7 @@
         <v>74</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>80</v>
@@ -21466,10 +21470,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -21492,7 +21496,7 @@
         <v>74</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L191" s="2"/>
       <c r="M191" s="2"/>
@@ -21545,7 +21549,7 @@
         <v>74</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>80</v>
@@ -21565,10 +21569,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -21591,7 +21595,7 @@
         <v>74</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L192" s="2"/>
       <c r="M192" s="2"/>
@@ -21644,7 +21648,7 @@
         <v>74</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>80</v>
@@ -21664,10 +21668,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -21690,7 +21694,7 @@
         <v>74</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L193" s="2"/>
       <c r="M193" s="2"/>
@@ -21743,7 +21747,7 @@
         <v>74</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>80</v>
@@ -21763,10 +21767,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -21789,7 +21793,7 @@
         <v>74</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="L194" s="2"/>
       <c r="M194" s="2"/>
@@ -21842,7 +21846,7 @@
         <v>74</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>80</v>
@@ -21862,10 +21866,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -21888,7 +21892,7 @@
         <v>74</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L195" s="2"/>
       <c r="M195" s="2"/>
@@ -21941,7 +21945,7 @@
         <v>74</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>80</v>
@@ -21961,13 +21965,13 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D196" t="s" s="2">
         <v>74</v>
@@ -21989,10 +21993,10 @@
         <v>74</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M196" s="2"/>
       <c r="N196" s="2"/>
@@ -22044,7 +22048,7 @@
         <v>74</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>80</v>
@@ -22064,10 +22068,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -22165,10 +22169,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -22266,10 +22270,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -22367,10 +22371,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -22468,10 +22472,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -22571,10 +22575,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -22674,10 +22678,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -22777,10 +22781,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -22880,10 +22884,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -22981,10 +22985,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -23021,7 +23025,7 @@
         <v>74</v>
       </c>
       <c r="S206" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="T206" t="s" s="2">
         <v>74</v>
@@ -23040,7 +23044,7 @@
       </c>
       <c r="Y206" s="2"/>
       <c r="Z206" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AA206" t="s" s="2">
         <v>74</v>
@@ -23058,7 +23062,7 @@
         <v>74</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>75</v>
@@ -23078,10 +23082,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -23108,7 +23112,7 @@
       </c>
       <c r="L207" s="2"/>
       <c r="M207" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N207" s="2"/>
       <c r="O207" s="2"/>
@@ -23159,7 +23163,7 @@
         <v>74</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>80</v>
@@ -23179,10 +23183,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -23209,12 +23213,12 @@
       </c>
       <c r="L208" s="2"/>
       <c r="M208" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N208" s="2"/>
       <c r="O208" s="2"/>
       <c r="P208" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q208" s="2"/>
       <c r="R208" t="s" s="2">
@@ -23260,7 +23264,7 @@
         <v>74</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>80</v>
@@ -23280,10 +23284,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -23359,7 +23363,7 @@
         <v>74</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>80</v>
@@ -23379,10 +23383,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -23405,7 +23409,7 @@
         <v>74</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L210" s="2"/>
       <c r="M210" s="2"/>
@@ -23458,7 +23462,7 @@
         <v>74</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>80</v>
@@ -23478,10 +23482,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -23504,7 +23508,7 @@
         <v>74</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L211" s="2"/>
       <c r="M211" s="2"/>
@@ -23557,7 +23561,7 @@
         <v>74</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>80</v>
@@ -23577,10 +23581,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -23603,7 +23607,7 @@
         <v>74</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="L212" s="2"/>
       <c r="M212" s="2"/>
@@ -23656,7 +23660,7 @@
         <v>74</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>80</v>
@@ -23676,10 +23680,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -23702,7 +23706,7 @@
         <v>74</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L213" s="2"/>
       <c r="M213" s="2"/>
@@ -23755,7 +23759,7 @@
         <v>74</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>80</v>
@@ -23775,10 +23779,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -23801,7 +23805,7 @@
         <v>74</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="L214" s="2"/>
       <c r="M214" s="2"/>
@@ -23854,7 +23858,7 @@
         <v>74</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>80</v>
@@ -23874,10 +23878,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -23900,7 +23904,7 @@
         <v>74</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L215" s="2"/>
       <c r="M215" s="2"/>
@@ -23953,7 +23957,7 @@
         <v>74</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>80</v>
@@ -23973,10 +23977,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -23999,7 +24003,7 @@
         <v>74</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L216" s="2"/>
       <c r="M216" s="2"/>
@@ -24052,7 +24056,7 @@
         <v>74</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>80</v>
@@ -24072,10 +24076,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -24098,7 +24102,7 @@
         <v>74</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L217" s="2"/>
       <c r="M217" s="2"/>
@@ -24151,7 +24155,7 @@
         <v>74</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>80</v>
@@ -24171,10 +24175,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -24197,7 +24201,7 @@
         <v>74</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L218" s="2"/>
       <c r="M218" s="2"/>
@@ -24250,7 +24254,7 @@
         <v>74</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>80</v>
@@ -24270,10 +24274,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -24296,7 +24300,7 @@
         <v>74</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="L219" s="2"/>
       <c r="M219" s="2"/>
@@ -24349,7 +24353,7 @@
         <v>74</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>80</v>
@@ -24369,10 +24373,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -24395,7 +24399,7 @@
         <v>74</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L220" s="2"/>
       <c r="M220" s="2"/>
@@ -24448,7 +24452,7 @@
         <v>74</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>80</v>
@@ -24468,10 +24472,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -24494,7 +24498,7 @@
         <v>74</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="L221" s="2"/>
       <c r="M221" s="2"/>
@@ -24547,7 +24551,7 @@
         <v>74</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>80</v>
@@ -24567,10 +24571,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -24593,7 +24597,7 @@
         <v>74</v>
       </c>
       <c r="K222" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="L222" s="2"/>
       <c r="M222" s="2"/>
@@ -24646,7 +24650,7 @@
         <v>74</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>80</v>
@@ -24666,10 +24670,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -24692,7 +24696,7 @@
         <v>74</v>
       </c>
       <c r="K223" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="L223" s="2"/>
       <c r="M223" s="2"/>
@@ -24745,7 +24749,7 @@
         <v>74</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>80</v>
@@ -24765,10 +24769,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -24791,11 +24795,11 @@
         <v>74</v>
       </c>
       <c r="K224" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="L224" s="2"/>
       <c r="M224" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N224" s="2"/>
       <c r="O224" s="2"/>
@@ -24846,7 +24850,7 @@
         <v>74</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>80</v>
@@ -24866,10 +24870,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -24967,10 +24971,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -25068,10 +25072,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -25169,10 +25173,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -25270,10 +25274,10 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -25373,10 +25377,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -25476,10 +25480,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -25579,10 +25583,10 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -25682,10 +25686,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -25783,10 +25787,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -25820,7 +25824,7 @@
       </c>
       <c r="Q234" s="2"/>
       <c r="R234" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="S234" t="s" s="2">
         <v>74</v>
@@ -25842,7 +25846,7 @@
       </c>
       <c r="Y234" s="2"/>
       <c r="Z234" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AA234" t="s" s="2">
         <v>74</v>
@@ -25860,7 +25864,7 @@
         <v>74</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>80</v>
@@ -25880,10 +25884,10 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -25906,7 +25910,7 @@
         <v>74</v>
       </c>
       <c r="K235" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="L235" s="2"/>
       <c r="M235" s="2"/>
@@ -25959,7 +25963,7 @@
         <v>74</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>75</v>
@@ -25979,10 +25983,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -26005,7 +26009,7 @@
         <v>74</v>
       </c>
       <c r="K236" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="L236" s="2"/>
       <c r="M236" s="2"/>
@@ -26058,7 +26062,7 @@
         <v>74</v>
       </c>
       <c r="AF236" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG236" t="s" s="2">
         <v>80</v>
